--- a/docs/manual_test_cases.xlsx
+++ b/docs/manual_test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anton\Desktop\qa-automation-framework\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C4CF6B-B72F-425D-97F1-8C1B6631B33E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FE7146-24E3-417E-9F89-F92F44CCAF59}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28780" windowHeight="11590" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
